--- a/Unit_capacity.xlsx
+++ b/Unit_capacity.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\1. Work\1. Daily\Capacity Report\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F68FC0D8-FC45-41FD-A750-E87A32DFABC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68C6B68C-8A1A-4516-B6C2-B2DC727C8D9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="810" yWindow="-120" windowWidth="19800" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <t>Unit</t>
   </si>
@@ -75,10 +75,16 @@
     <t>Per Day Line Prod</t>
   </si>
   <si>
-    <t>Capacity</t>
-  </si>
-  <si>
     <t>Total</t>
+  </si>
+  <si>
+    <t>GTAL</t>
+  </si>
+  <si>
+    <t>Capacity (Monthly)</t>
+  </si>
+  <si>
+    <t>Capacity (Daily)</t>
   </si>
 </sst>
 </file>
@@ -137,12 +143,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -423,36 +435,40 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="6" max="6" width="9.85546875" customWidth="1"/>
     <col min="7" max="7" width="10.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:8" s="6" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G1" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -463,11 +479,11 @@
         <v>0.71</v>
       </c>
       <c r="D2" s="2">
-        <v>1326</v>
+        <v>1340</v>
       </c>
       <c r="E2" s="3">
         <f>(D2/20)*26</f>
-        <v>1723.8</v>
+        <v>1742</v>
       </c>
       <c r="F2" s="3">
         <f>(25*C2*10*60)/(B2)</f>
@@ -475,10 +491,14 @@
       </c>
       <c r="G2" s="3">
         <f>E2*F2</f>
-        <v>2622638.5714285714</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2650328.5714285714</v>
+      </c>
+      <c r="H2" s="3">
+        <f>F2*(D2/20)</f>
+        <v>101935.71428571428</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -496,15 +516,19 @@
         <v>790.4</v>
       </c>
       <c r="F3" s="3">
-        <f t="shared" ref="F3:F8" si="1">(25*C3*10*60)/(B3)</f>
+        <f t="shared" ref="F3:F9" si="1">(25*C3*10*60)/(B3)</f>
         <v>1850</v>
       </c>
       <c r="G3" s="3">
-        <f t="shared" ref="G3:G8" si="2">E3*F3</f>
+        <f t="shared" ref="G3:G9" si="2">E3*F3</f>
         <v>1462240</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H3" s="3">
+        <f>F3*(D3/20)</f>
+        <v>56240</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
@@ -529,8 +553,12 @@
         <f t="shared" si="2"/>
         <v>2163398.8235294116</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H4" s="3">
+        <f>F4*(D4/20)</f>
+        <v>83207.647058823524</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
@@ -555,8 +583,12 @@
         <f t="shared" si="2"/>
         <v>3369600</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H5" s="3">
+        <f>F5*(D5/20)</f>
+        <v>129600</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
@@ -581,8 +613,12 @@
         <f t="shared" si="2"/>
         <v>2139280</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H6" s="3">
+        <f>F6*(D6/20)</f>
+        <v>82280</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
@@ -607,8 +643,12 @@
         <f t="shared" si="2"/>
         <v>2128400</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H7" s="3">
+        <f>F7*(D7/20)</f>
+        <v>81861.538461538454</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>7</v>
       </c>
@@ -633,28 +673,66 @@
         <f t="shared" si="2"/>
         <v>3678315.789473684</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H8" s="3">
+        <f>F8*(D8/20)</f>
+        <v>141473.68421052632</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1">
-        <f>SUM(D2:D8)</f>
-        <v>8973</v>
-      </c>
-      <c r="E9" s="4">
-        <f t="shared" ref="E9:G9" si="3">SUM(E2:E8)</f>
-        <v>11664.9</v>
-      </c>
-      <c r="F9" s="4">
-        <f t="shared" si="3"/>
-        <v>11491.133263021808</v>
-      </c>
-      <c r="G9" s="4">
-        <f t="shared" si="3"/>
-        <v>17563873.184431665</v>
+      <c r="B9" s="2">
+        <v>6</v>
+      </c>
+      <c r="C9" s="2">
+        <v>0.7</v>
+      </c>
+      <c r="D9" s="2">
+        <v>792</v>
+      </c>
+      <c r="E9" s="3">
+        <f t="shared" si="0"/>
+        <v>1029.6000000000001</v>
+      </c>
+      <c r="F9" s="3">
+        <f t="shared" si="1"/>
+        <v>1750</v>
+      </c>
+      <c r="G9" s="3">
+        <f t="shared" si="2"/>
+        <v>1801800.0000000002</v>
+      </c>
+      <c r="H9" s="3">
+        <f>F9*(D9/20)</f>
+        <v>69300</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1">
+        <f>SUM(D2:D9)</f>
+        <v>9779</v>
+      </c>
+      <c r="E10" s="4">
+        <f>SUM(E2:E9)</f>
+        <v>12712.7</v>
+      </c>
+      <c r="F10" s="4">
+        <f>SUM(F2:F9)</f>
+        <v>13241.133263021808</v>
+      </c>
+      <c r="G10" s="4">
+        <f>SUM(G2:G9)</f>
+        <v>19393363.184431665</v>
+      </c>
+      <c r="H10" s="4">
+        <f>SUM(H2:H9)</f>
+        <v>745898.5840166026</v>
       </c>
     </row>
   </sheetData>
